--- a/arquivos/tabela_basica.xlsx
+++ b/arquivos/tabela_basica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thiago\Documents\thiagogalvao.github.io\arquivos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CEBRAC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0B5A92-4BCA-47A0-9D02-A2B4C9D128A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365505AA-111E-418E-A7CC-E3E15649B118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{D639934A-5EB6-480F-A41D-4B69CF4558DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{D639934A-5EB6-480F-A41D-4B69CF4558DF}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUTOS" sheetId="1" r:id="rId1"/>
@@ -151,8 +151,8 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -168,7 +168,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7372349" y="0"/>
-          <a:ext cx="6496051" cy="4324351"/>
+          <a:ext cx="6496051" cy="5391150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -746,7 +746,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>4. Insira uma coluna de estoque entre nome e preço e preencha com números aleatórios.</a:t>
+            <a:t>4. Insira uma coluna "QUANTIDADE VENDIDA" entre "PREÇO UNITÁRIO" e "CATEGORIA" e preencha com números aleatórios.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -803,7 +803,64 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>5. Crie uma nova aba para a coluna clientes e siga os exercícios da folha.</a:t>
+            <a:t>5. Crie uma coluna "TOTAL VENDIDO" e calcule o total vendido para cada linha.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="1" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>6. Crie uma nova aba para os dados de clientes e siga os exercícios da folha.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
